--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:25:22+00:00</t>
+    <t>2025-07-07T15:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="691">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:26:46+00:00</t>
+    <t>2025-10-08T07:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -710,7 +710,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -766,14 +766,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Patient.extension:multipleBirth</t>
@@ -789,7 +785,7 @@
     <t>Rang Gémellaire</t>
   </si>
   <si>
-    <t>Extension crée pour exprimer le rang gémellaire, notamment utle dans le cadre des attestations de droits à l'assurance maladie. Cette extension implemente l'élément PatientMultipleBirth de R5 https://www.hl7.org/fhir/patient-definitions.html#Patient.multipleBirth_x.</t>
+    <t>Extension créée pour exprimer le rang gémellaire, notamment utile dans le cadre des attestations de droits à l'assurance maladie. Cette extension implemente l'élément PatientMultipleBirth de R5 https://www.hl7.org/fhir/patient-definitions.html#Patient.multipleBirth_x.</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -815,7 +811,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS au statut qualifié, il est nécessaire de respecter la conformité au profil FRCorePatientINS. Les identifiants NIR et NIA ne sont définis que dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -828,7 +824,7 @@
 </t>
   </si>
   <si>
-    <t>slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
+    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
   </si>
   <si>
     <t>id</t>
@@ -1151,7 +1147,7 @@
     <t>PI</t>
   </si>
   <si>
-    <t>Hospital assigned patient identifier | IPP</t>
+    <t>Hospital assigned patient identifier | Identifiant Patient Permanent (IPP).</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -1163,7 +1159,10 @@
     <t>Patient.identifier:PI.use</t>
   </si>
   <si>
-    <t>usual</t>
+    <t>La valeur old permet d'identifier des IPP désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use-pi</t>
   </si>
   <si>
     <t>Patient.identifier:PI.type</t>
@@ -1339,6 +1338,9 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>usual</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -2528,10 +2530,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.48828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="64.48046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5215,7 +5217,7 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -5264,7 +5266,7 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>105</v>
@@ -5330,7 +5332,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>82</v>
@@ -5677,7 +5679,7 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>102</v>
@@ -5700,13 +5702,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
@@ -5728,13 +5730,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5817,10 +5819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5846,16 +5848,16 @@
         <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5904,7 +5906,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5936,10 +5938,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5962,17 +5964,17 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6009,10 +6011,10 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AC30" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
@@ -6021,7 +6023,7 @@
         <v>117</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6036,16 +6038,16 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6053,10 +6055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6168,10 +6170,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6285,10 +6287,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6314,16 +6316,16 @@
         <v>170</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6348,31 +6350,31 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6387,7 +6389,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6404,10 +6406,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6430,19 +6432,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6471,25 +6473,25 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6504,7 +6506,7 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -6513,7 +6515,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6521,10 +6523,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6550,16 +6552,16 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6572,43 +6574,43 @@
         <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6623,16 +6625,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6640,10 +6642,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6669,13 +6671,13 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6689,43 +6691,43 @@
         <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6740,16 +6742,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6757,10 +6759,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6783,13 +6785,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6840,7 +6842,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6855,16 +6857,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6872,10 +6874,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6898,16 +6900,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6957,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6972,16 +6974,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6989,13 +6991,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -7017,17 +7019,17 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7076,7 +7078,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7091,16 +7093,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7108,10 +7110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7223,10 +7225,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7340,10 +7342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7369,16 +7371,16 @@
         <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7388,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7403,31 +7405,31 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7442,7 +7444,7 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
@@ -7459,10 +7461,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7485,19 +7487,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7507,7 +7509,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7526,25 +7528,25 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7559,7 +7561,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
@@ -7568,7 +7570,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7576,10 +7578,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7605,16 +7607,16 @@
         <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7624,46 +7626,46 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T44" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7678,16 +7680,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7695,10 +7697,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7724,13 +7726,13 @@
         <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7744,43 +7746,43 @@
         <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7795,16 +7797,16 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7812,10 +7814,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7838,13 +7840,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7895,7 +7897,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7910,16 +7912,16 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7927,10 +7929,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7953,16 +7955,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8012,7 +8014,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8027,16 +8029,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8044,13 +8046,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
@@ -8072,17 +8074,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8131,7 +8133,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8146,16 +8148,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8163,10 +8165,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8278,10 +8280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8395,10 +8397,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8424,16 +8426,16 @@
         <v>170</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8443,7 +8445,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8458,31 +8460,31 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8497,7 +8499,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
@@ -8514,10 +8516,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8540,19 +8542,19 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8562,7 +8564,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8581,25 +8583,25 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8614,7 +8616,7 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -8623,7 +8625,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8631,10 +8633,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8660,16 +8662,16 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8679,46 +8681,46 @@
         <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8733,16 +8735,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8750,10 +8752,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8779,13 +8781,13 @@
         <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8799,43 +8801,43 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8850,16 +8852,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8867,10 +8869,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8893,13 +8895,13 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8950,7 +8952,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8965,16 +8967,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8982,10 +8984,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9008,16 +9010,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9067,7 +9069,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9082,16 +9084,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9099,13 +9101,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
@@ -9127,17 +9129,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9186,7 +9188,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9201,16 +9203,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9218,10 +9220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9333,10 +9335,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9450,10 +9452,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9479,16 +9481,16 @@
         <v>170</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9498,7 +9500,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9513,31 +9515,31 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y60" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y60" t="s" s="2">
+      <c r="Z60" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9552,7 +9554,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
@@ -9569,10 +9571,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9595,19 +9597,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9617,7 +9619,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9636,25 +9638,25 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9669,7 +9671,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -9678,7 +9680,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9686,10 +9688,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9715,16 +9717,16 @@
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9734,46 +9736,46 @@
         <v>82</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T62" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9788,16 +9790,16 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9805,10 +9807,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9834,13 +9836,13 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9854,43 +9856,43 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9905,16 +9907,16 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9922,10 +9924,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9948,13 +9950,13 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10005,7 +10007,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10020,16 +10022,16 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10037,10 +10039,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10063,16 +10065,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10122,7 +10124,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10137,16 +10139,16 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10154,13 +10156,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C66" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
@@ -10182,17 +10184,17 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10241,7 +10243,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10256,16 +10258,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10273,10 +10275,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10388,10 +10390,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10505,10 +10507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10534,16 +10536,16 @@
         <v>170</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="N69" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10553,46 +10555,44 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y69" s="2"/>
+      <c r="Z69" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="T69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10607,7 +10607,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -10627,7 +10627,7 @@
         <v>364</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10650,19 +10650,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10691,25 +10691,25 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10724,7 +10724,7 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
@@ -10733,7 +10733,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10744,7 +10744,7 @@
         <v>366</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10770,16 +10770,16 @@
         <v>132</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10792,43 +10792,43 @@
         <v>82</v>
       </c>
       <c r="T71" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10843,16 +10843,16 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10863,7 +10863,7 @@
         <v>367</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10889,13 +10889,13 @@
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10909,43 +10909,43 @@
         <v>82</v>
       </c>
       <c r="T72" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10960,16 +10960,16 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10980,7 +10980,7 @@
         <v>368</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11003,13 +11003,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11060,7 +11060,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11075,16 +11075,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11095,7 +11095,7 @@
         <v>369</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11118,16 +11118,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11177,7 +11177,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11192,16 +11192,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11212,7 +11212,7 @@
         <v>370</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>371</v>
@@ -11237,17 +11237,17 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>372</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11296,7 +11296,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11311,16 +11311,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11331,7 +11331,7 @@
         <v>373</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11446,7 +11446,7 @@
         <v>374</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11563,7 +11563,7 @@
         <v>375</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11589,16 +11589,16 @@
         <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11608,7 +11608,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11623,31 +11623,31 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z78" t="s" s="2">
+      <c r="AA78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11662,7 +11662,7 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>82</v>
@@ -11682,7 +11682,7 @@
         <v>376</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11705,19 +11705,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11746,25 +11746,25 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11779,7 +11779,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
@@ -11788,7 +11788,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11799,7 +11799,7 @@
         <v>378</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11825,16 +11825,16 @@
         <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11847,43 +11847,43 @@
         <v>82</v>
       </c>
       <c r="T80" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11898,16 +11898,16 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11918,7 +11918,7 @@
         <v>379</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11944,13 +11944,13 @@
         <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11964,43 +11964,43 @@
         <v>82</v>
       </c>
       <c r="T81" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12015,16 +12015,16 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12035,7 +12035,7 @@
         <v>380</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12058,13 +12058,13 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12115,7 +12115,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12130,16 +12130,16 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12150,7 +12150,7 @@
         <v>381</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12173,16 +12173,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12232,7 +12232,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12247,16 +12247,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12903,7 +12903,7 @@
         <v>82</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>82</v>
@@ -12918,13 +12918,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12942,7 +12942,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12957,7 +12957,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -12966,7 +12966,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12974,10 +12974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13003,16 +13003,16 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13061,7 +13061,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13076,7 +13076,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13085,7 +13085,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13093,14 +13093,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13122,13 +13122,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13178,7 +13178,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13193,7 +13193,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13202,7 +13202,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13210,14 +13210,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13239,13 +13239,13 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13295,7 +13295,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13310,7 +13310,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13319,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13327,10 +13327,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13356,10 +13356,10 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13410,7 +13410,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13425,7 +13425,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13434,7 +13434,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13442,10 +13442,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13471,10 +13471,10 @@
         <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13525,7 +13525,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13540,7 +13540,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>82</v>
@@ -13549,7 +13549,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13557,10 +13557,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13583,17 +13583,17 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13642,7 +13642,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13657,7 +13657,7 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>82</v>
@@ -13666,7 +13666,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13674,13 +13674,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>391</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>82</v>
@@ -13705,10 +13705,10 @@
         <v>403</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>395</v>
@@ -13795,7 +13795,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>407</v>
@@ -13910,7 +13910,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>409</v>
@@ -14027,13 +14027,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>409</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14055,13 +14055,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14144,7 +14144,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>411</v>
@@ -14192,7 +14192,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14207,13 +14207,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14231,7 +14231,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14246,7 +14246,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14255,7 +14255,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14263,10 +14263,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14292,16 +14292,16 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14350,7 +14350,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14365,7 +14365,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14374,7 +14374,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14382,14 +14382,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14411,13 +14411,13 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14467,7 +14467,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14482,7 +14482,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14491,7 +14491,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14499,14 +14499,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14528,13 +14528,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14584,7 +14584,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14599,7 +14599,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14608,7 +14608,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14616,10 +14616,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14645,10 +14645,10 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14699,7 +14699,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14714,7 +14714,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -14723,7 +14723,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14731,10 +14731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14760,10 +14760,10 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14814,7 +14814,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14829,7 +14829,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -14838,7 +14838,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14846,10 +14846,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14872,17 +14872,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14931,7 +14931,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14946,7 +14946,7 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>82</v>
@@ -14955,7 +14955,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14963,10 +14963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14989,19 +14989,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15050,7 +15050,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15065,16 +15065,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15082,10 +15082,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15111,16 +15111,16 @@
         <v>170</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15145,13 +15145,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15169,7 +15169,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15184,16 +15184,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15201,10 +15201,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15227,19 +15227,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15288,7 +15288,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15303,27 +15303,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15346,19 +15346,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15407,7 +15407,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15422,7 +15422,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>108</v>
@@ -15431,7 +15431,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15439,10 +15439,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15468,16 +15468,16 @@
         <v>237</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15526,7 +15526,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15541,16 +15541,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15558,10 +15558,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15584,17 +15584,17 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15641,7 +15641,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15656,16 +15656,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15673,10 +15673,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15699,19 +15699,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15760,7 +15760,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15775,7 +15775,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15784,7 +15784,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15792,10 +15792,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15818,19 +15818,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15879,7 +15879,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15894,7 +15894,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15903,7 +15903,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -15911,10 +15911,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15937,19 +15937,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -15998,7 +15998,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16010,10 +16010,10 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>108</v>
@@ -16030,10 +16030,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16145,10 +16145,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16258,13 +16258,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="B118" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="C118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16286,13 +16286,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16375,13 +16375,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
@@ -16403,13 +16403,13 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16492,14 +16492,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16521,16 +16521,16 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16579,7 +16579,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16611,10 +16611,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16637,17 +16637,17 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16675,10 +16675,10 @@
         <v>152</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16694,7 +16694,7 @@
         <v>117</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16709,7 +16709,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16718,7 +16718,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16726,13 +16726,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16754,17 +16754,17 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16811,7 +16811,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16826,7 +16826,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16835,7 +16835,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16843,13 +16843,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -16871,17 +16871,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16910,7 +16910,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16928,7 +16928,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16943,7 +16943,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16952,7 +16952,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16960,10 +16960,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16989,14 +16989,14 @@
         <v>392</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17045,7 +17045,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17069,7 +17069,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17077,10 +17077,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17103,19 +17103,19 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17164,7 +17164,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17179,7 +17179,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17188,7 +17188,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17196,10 +17196,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17222,17 +17222,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17281,7 +17281,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17296,7 +17296,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17305,7 +17305,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17313,10 +17313,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17342,14 +17342,14 @@
         <v>170</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17374,13 +17374,13 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17398,7 +17398,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17413,7 +17413,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17422,7 +17422,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17430,10 +17430,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17456,17 +17456,17 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17515,7 +17515,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17524,13 +17524,13 @@
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17539,7 +17539,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17547,10 +17547,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17573,13 +17573,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17630,7 +17630,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17645,7 +17645,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>108</v>
@@ -17662,10 +17662,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17688,19 +17688,19 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17749,7 +17749,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17764,10 +17764,10 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
@@ -17781,10 +17781,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17896,10 +17896,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18013,14 +18013,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18042,16 +18042,16 @@
         <v>111</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18100,7 +18100,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18132,10 +18132,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18158,19 +18158,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18219,7 +18219,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>90</v>
@@ -18234,16 +18234,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18251,10 +18251,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18280,16 +18280,16 @@
         <v>383</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18338,7 +18338,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18353,16 +18353,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18370,14 +18370,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18396,16 +18396,16 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18455,7 +18455,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18470,7 +18470,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>108</v>
@@ -18479,7 +18479,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18487,10 +18487,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18513,19 +18513,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18574,7 +18574,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18589,10 +18589,10 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18606,10 +18606,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18632,19 +18632,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18693,7 +18693,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18708,7 +18708,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>108</v>
@@ -18725,10 +18725,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18840,10 +18840,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18957,14 +18957,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18986,16 +18986,16 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19044,7 +19044,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19076,10 +19076,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19102,16 +19102,16 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19161,7 +19161,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19176,7 +19176,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
@@ -19185,7 +19185,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19193,10 +19193,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19222,10 +19222,10 @@
         <v>170</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19252,13 +19252,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19276,7 +19276,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19291,7 +19291,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>108</v>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:41:56+00:00</t>
+    <t>2025-10-08T15:42:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
